--- a/Promos_Tracker.xlsx
+++ b/Promos_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D2C0C8-1A8C-4FD3-9531-77297D6E3996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DAA6D6-C184-4AD5-AD1F-7257C9015271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="23385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="130">
   <si>
     <t>Promo ID</t>
   </si>
@@ -386,6 +386,30 @@
   </si>
   <si>
     <t>Bad Dude Wayne</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Skye</t>
+  </si>
+  <si>
+    <t>Day 4</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Marina</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Cami</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Juniper</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Leaf</t>
+  </si>
+  <si>
+    <t>Pikachu Fan Raye</t>
+  </si>
+  <si>
+    <t>Pikachu Mum</t>
   </si>
 </sst>
 </file>
@@ -815,6 +839,12 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -851,6 +881,12 @@
       <c r="B5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1092,6 +1128,12 @@
       <c r="B25" t="s">
         <v>54</v>
       </c>
+      <c r="C25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
@@ -1100,6 +1142,12 @@
       <c r="B26" t="s">
         <v>56</v>
       </c>
+      <c r="C26" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1108,6 +1156,12 @@
       <c r="B27" t="s">
         <v>5</v>
       </c>
+      <c r="C27" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1116,6 +1170,12 @@
       <c r="B28" t="s">
         <v>5</v>
       </c>
+      <c r="C28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1123,6 +1183,12 @@
       </c>
       <c r="B29" t="s">
         <v>60</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">

--- a/Promos_Tracker.xlsx
+++ b/Promos_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DAA6D6-C184-4AD5-AD1F-7257C9015271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2867A18-14F7-4B7E-BC13-963DACC6D677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="23385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14445" yWindow="2145" windowWidth="43200" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="133">
   <si>
     <t>Promo ID</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Jigglypuff</t>
   </si>
   <si>
-    <t>basep-8</t>
-  </si>
-  <si>
     <t>Mew</t>
   </si>
   <si>
@@ -410,6 +407,18 @@
   </si>
   <si>
     <t>Pikachu Mum</t>
+  </si>
+  <si>
+    <t>Light Engineer Chase</t>
+  </si>
+  <si>
+    <t>Night 5</t>
+  </si>
+  <si>
+    <t>Team Rocket Boss Giovanni</t>
+  </si>
+  <si>
+    <t>Evening 5</t>
   </si>
 </sst>
 </file>
@@ -810,12 +819,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -840,10 +849,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -854,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -868,10 +877,10 @@
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,10 +891,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -895,6 +904,12 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -904,10 +919,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
         <v>112</v>
-      </c>
-      <c r="D7" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -918,18 +933,24 @@
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" t="s">
-        <v>22</v>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -937,41 +958,41 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -979,21 +1000,27 @@
         <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1001,93 +1028,93 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>119</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>110</v>
+        <v>38</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>111</v>
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -1095,13 +1122,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -1109,44 +1136,44 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>129</v>
+        <v>55</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" t="s">
         <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,7 +1187,7 @@
         <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1168,163 +1195,157 @@
         <v>58</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1332,7 +1353,7 @@
         <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -1340,7 +1361,7 @@
         <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -1348,47 +1369,39 @@
         <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
         <v>106</v>
-      </c>
-      <c r="B54" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
